--- a/outputs/results/result2_filled.xlsx
+++ b/outputs/results/result2_filled.xlsx
@@ -1,248 +1,204 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="computed_solution" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">      工件
-原材料</t>
-  </si>
-  <si>
-    <t>J01</t>
-  </si>
-  <si>
-    <t>J02</t>
-  </si>
-  <si>
-    <t>J03</t>
-  </si>
-  <si>
-    <t>J04</t>
-  </si>
-  <si>
-    <t>J05</t>
-  </si>
-  <si>
-    <t>J06</t>
-  </si>
-  <si>
-    <t>J07</t>
-  </si>
-  <si>
-    <t>收益</t>
-  </si>
-  <si>
-    <t>L01</t>
-  </si>
-  <si>
-    <t>L02</t>
-  </si>
-  <si>
-    <t>L03</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="25">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E75B6"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="34">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="35">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -439,8 +395,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -578,172 +540,184 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -797,11 +771,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1053,348 +1090,1533 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B2:J19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="12.2727272727273" customWidth="1"/>
+    <col width="12.2727272727273" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.75"/>
-    <row r="3" ht="28" customHeight="1" spans="2:10">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="17" customHeight="1" spans="2:10">
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+    <row r="1"/>
+    <row r="2" ht="14.75" customHeight="1" s="5"/>
+    <row r="3" ht="28" customHeight="1" s="5">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      工件
+原材料</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>J06</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>J07</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>收益</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1" s="5">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J4" s="4">
         <f>C4*620+D4*780+E4*880+F4*1850+G4*2520+H4*1000+I4*540</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1" spans="2:10">
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1" s="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J5" s="4">
-        <f t="shared" ref="J5:J18" si="0">C5*620+D5*780+E5*880+F5*1850+G5*2520+H5*1000+I5*540</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1" spans="2:10">
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <f>C5*620+D5*780+E5*880+F5*1850+G5*2520+H5*1000+I5*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" s="5">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J6" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1" spans="2:10">
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+        <f>C6*620+D6*780+E6*880+F6*1850+G6*2520+H6*1000+I6*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" s="5">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J7" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1" spans="2:10">
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <f>C7*620+D7*780+E7*880+F7*1850+G7*2520+H7*1000+I7*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1" s="5">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J8" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1" spans="2:10">
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+        <f>C8*620+D8*780+E8*880+F8*1850+G8*2520+H8*1000+I8*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="5">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J9" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1" spans="2:10">
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+        <f>C9*620+D9*780+E9*880+F9*1850+G9*2520+H9*1000+I9*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1" s="5">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J10" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1" spans="2:10">
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+        <f>C10*620+D10*780+E10*880+F10*1850+G10*2520+H10*1000+I10*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="5">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J11" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1" spans="2:10">
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+        <f>C11*620+D11*780+E11*880+F11*1850+G11*2520+H11*1000+I11*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1" s="5">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J12" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1" spans="2:10">
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+        <f>C12*620+D12*780+E12*880+F12*1850+G12*2520+H12*1000+I12*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1" s="5">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J13" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1" spans="2:10">
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+        <f>C13*620+D13*780+E13*880+F13*1850+G13*2520+H13*1000+I13*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1" s="5">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J14" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1" spans="2:10">
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+        <f>C14*620+D14*780+E14*880+F14*1850+G14*2520+H14*1000+I14*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1" s="5">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J15" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1" spans="2:10">
-      <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+        <f>C15*620+D15*780+E15*880+F15*1850+G15*2520+H15*1000+I15*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="5">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J16" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1" spans="2:10">
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+        <f>C16*620+D16*780+E16*880+F16*1850+G16*2520+H16*1000+I16*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="5">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J17" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1" spans="2:10">
-      <c r="B18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+        <f>C17*620+D17*780+E17*880+F17*1850+G17*2520+H17*1000+I17*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1" s="5">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="J18" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="2" t="s">
-        <v>12</v>
+        <f>C18*620+D18*780+E18*880+F18*1850+G18*2520+H18*1000+I18*540</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
       </c>
       <c r="C19" s="2">
         <f>SUM(C4:C18)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D19" s="2">
-        <f t="shared" ref="D19:J19" si="1">SUM(D4:D18)</f>
-        <v>0</v>
+        <f>SUM(D4:D18)</f>
+        <v/>
       </c>
       <c r="E19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(E4:E18)</f>
+        <v/>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(F4:F18)</f>
+        <v/>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(G4:G18)</f>
+        <v/>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(H4:H18)</f>
+        <v/>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(I4:I18)</f>
+        <v/>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>SUM(J4:J18)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="5" min="1" max="1"/>
+    <col width="22" customWidth="1" style="5" min="2" max="2"/>
+    <col width="22" customWidth="1" style="5" min="3" max="3"/>
+    <col width="22" customWidth="1" style="5" min="4" max="4"/>
+    <col width="22" customWidth="1" style="5" min="5" max="5"/>
+    <col width="22" customWidth="1" style="5" min="6" max="6"/>
+    <col width="22" customWidth="1" style="5" min="7" max="7"/>
+    <col width="22" customWidth="1" style="5" min="8" max="8"/>
+    <col width="22" customWidth="1" style="5" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Computed Solution - PROBLEM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Basic Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>OPTIMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Objective Value</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>742400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>742,400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Total Used Volume</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>73,040,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Total Waste Volume</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2,710,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Total Material Volume</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>75,750,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Material Utilization</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>96.42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Waste Gap Ratio</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>3.5776%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Utilization Gap to 100%</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>3.5776%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Upper Bound (utilization)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>852,187.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Lower Bound</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>742,400.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>12.8830%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Solve Time (s)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Optimality Note</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Pattern-library optimal (not necessarily global optimal without complete pattern enumeration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Runtime Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>pattern_generation_time</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>1.87s</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>master_solve_time</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>1.99s</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>plotting_time_problem1</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>13.38s</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>plotting_time_problem2</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>22.28s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>excel_writing_time</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>0.22s</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Piece Production Quantities</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Volume/Unit</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Total Volume</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Unit Profit</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>64000</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2560000</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>24960</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>9360000</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>880</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>91520</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2880000</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>29600</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>40320</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>J06</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>424</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>42400000</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>424000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>J07</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>210</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>10080000</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>540</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>113400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Material Utilization Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Volume/Material</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Total Volume</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>18750000</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>16760000</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>1990000</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>89.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>11280000</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>720000</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>94.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Pattern Usage Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Pattern ID</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Times Used</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pieces</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>89.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>3340000</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>89.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>90.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/results/result2_filled.xlsx
+++ b/outputs/results/result2_filled.xlsx
@@ -1095,13 +1095,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="B3:K19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12.2727272727273" customWidth="1" style="5" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="14.75" customHeight="1" s="5"/>
     <row r="3" ht="28" customHeight="1" s="5">
       <c r="B3" s="1" t="inlineStr">
@@ -1157,32 +1156,26 @@
           <t>L01</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4">
         <f>C4*620+D4*780+E4*880+F4*1850+G4*2520+H4*1000+I4*540</f>
@@ -1195,32 +1188,26 @@
           <t>L01</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>424</v>
+        <v>90</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4">
         <f>C5*620+D5*780+E5*880+F5*1850+G5*2520+H5*1000+I5*540</f>
@@ -1233,32 +1220,26 @@
           <t>L01</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>424</v>
+        <v>90</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4">
         <f>C6*620+D6*780+E6*880+F6*1850+G6*2520+H6*1000+I6*540</f>
@@ -1271,32 +1252,26 @@
           <t>L01</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>424</v>
+        <v>90</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4">
         <f>C7*620+D7*780+E7*880+F7*1850+G7*2520+H7*1000+I7*540</f>
@@ -1309,32 +1284,26 @@
           <t>L01</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>424</v>
+        <v>90</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4">
         <f>C8*620+D8*780+E8*880+F8*1850+G8*2520+H8*1000+I8*540</f>
@@ -1347,32 +1316,26 @@
           <t>L02</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="J9" s="4">
         <f>C9*620+D9*780+E9*880+F9*1850+G9*2520+H9*1000+I9*540</f>
@@ -1385,32 +1348,26 @@
           <t>L02</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="J10" s="4">
         <f>C10*620+D10*780+E10*880+F10*1850+G10*2520+H10*1000+I10*540</f>
@@ -1423,32 +1380,26 @@
           <t>L02</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="J11" s="4">
         <f>C11*620+D11*780+E11*880+F11*1850+G11*2520+H11*1000+I11*540</f>
@@ -1461,32 +1412,26 @@
           <t>L02</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="J12" s="4">
         <f>C12*620+D12*780+E12*880+F12*1850+G12*2520+H12*1000+I12*540</f>
@@ -1499,32 +1444,26 @@
           <t>L02</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>89.39%</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="J13" s="4">
         <f>C13*620+D13*780+E13*880+F13*1850+G13*2520+H13*1000+I13*540</f>
@@ -1537,32 +1476,26 @@
           <t>L03</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4">
         <f>C14*620+D14*780+E14*880+F14*1850+G14*2520+H14*1000+I14*540</f>
@@ -1575,32 +1508,26 @@
           <t>L03</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4">
         <f>C15*620+D15*780+E15*880+F15*1850+G15*2520+H15*1000+I15*540</f>
@@ -1613,32 +1540,26 @@
           <t>L03</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>424</v>
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4">
         <f>C16*620+D16*780+E16*880+F16*1850+G16*2520+H16*1000+I16*540</f>
@@ -1651,32 +1572,26 @@
           <t>L03</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>424</v>
+        <v>1</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4">
         <f>C17*620+D17*780+E17*880+F17*1850+G17*2520+H17*1000+I17*540</f>
@@ -1689,32 +1604,26 @@
           <t>L03</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>94.00%</t>
-        </is>
+      <c r="C18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4">
         <f>C18*620+D18*780+E18*880+F18*1850+G18*2520+H18*1000+I18*540</f>
@@ -1774,9 +1683,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -1790,9 +1697,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -1804,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -1852,7 +1757,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>742400.00</t>
+          <t>745680.00</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1769,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>742,400.00</t>
+          <t>745,680.00</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1781,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>73,040,000</t>
+          <t>72,512,000</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1793,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2,710,000</t>
+          <t>3,238,000</t>
         </is>
       </c>
     </row>
@@ -1912,521 +1817,533 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>96.42%</t>
+          <t>95.7254%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Waste Gap Ratio</t>
+          <t>Utilization Gap to 100%</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>3.5776%</t>
+          <t>4.2746%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Utilization Gap to 100%</t>
+          <t>Upper Bound</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>3.5776%</t>
+          <t>852,187.5000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Upper Bound (utilization)</t>
+          <t>Lower Bound</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>852,187.50</t>
+          <t>745,680.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Lower Bound</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>742,400.00</t>
+          <t>12.4981%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Solve Time (s)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>12.8830%</t>
+          <t>0.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Solve Time (s)</t>
+          <t>Pattern-Library Optimal</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>0.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Optimality Note</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Pattern-library optimal (not necessarily global optimal without complete pattern enumeration)</t>
+          <t>CP-SAT OPTIMAL within generated pattern library</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Runtime Breakdown</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Runtime Breakdown</t>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>pattern_generation_time</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>94.71s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>pattern_generation_time</t>
+          <t>master_solve_time</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>1.87s</t>
+          <t>94.78s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>master_solve_time</t>
+          <t>plotting_time_problem1</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>1.99s</t>
+          <t>9.72s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>plotting_time_problem1</t>
+          <t>plotting_time_problem2</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>13.38s</t>
+          <t>14.10s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>plotting_time_problem2</t>
+          <t>excel_writing_time</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>22.28s</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>excel_writing_time</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>0.22s</t>
+          <t>0.14s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Piece Production Quantities</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Piece Production Quantities</t>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Unit Volume</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Total Volume</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Unit Profit</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Piece</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Volume/Unit</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Total Volume</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>Unit Profit</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Total Profit</t>
-        </is>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>64000</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>18600</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
         <v>30</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>64000</v>
+        <v>80000</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1920000</v>
+        <v>2400000</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>620</v>
+        <v>780</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>18600</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2560000</v>
+        <v>9000000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>780</v>
+        <v>880</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>24960</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>90000</v>
+        <v>180000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>9360000</v>
+        <v>2160000</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>880</v>
+        <v>1850</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>91520</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J05</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
         <v>16</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>180000</v>
+        <v>240000</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2880000</v>
+        <v>3840000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1850</v>
+        <v>2520</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>29600</v>
+        <v>40320</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J06</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>16</v>
+        <v>362</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>240000</v>
+        <v>100000</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3840000</v>
+        <v>36200000</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>2520</v>
+        <v>1000</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>40320</v>
+        <v>362000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>J06</t>
+          <t>J07</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>100000</v>
+        <v>48000</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>42400000</v>
+        <v>16992000</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>424000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>J07</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n">
-        <v>210</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>48000</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>10080000</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>540</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>113400</v>
+        <v>191160</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Material Utilization Breakdown</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Material Utilization Breakdown</t>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Unit Volume</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Total Volume</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Volume/Material</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Total Volume</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Used Volume</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>Waste</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Utilization</t>
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="B38" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C38" s="9" t="n">
-        <v>9000000</v>
+        <v>3750000</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>45000000</v>
+        <v>18750000</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>45000000</v>
+        <v>16800000</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0</v>
+        <v>1950000</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>89.60%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L03</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C39" s="9" t="n">
-        <v>3750000</v>
+        <v>2400000</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>18750000</v>
+        <v>12000000</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>16760000</v>
+        <v>10712000</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1990000</v>
+        <v>1288000</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>89.39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>11280000</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>720000</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>94.00%</t>
+          <t>89.27%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Pattern Usage Details</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Pattern Usage Details</t>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Pattern ID</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Times Used</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pieces</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Pattern ID</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Times Used</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Pieces</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Used Volume</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>Utilization</t>
+      <c r="A43" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
@@ -2434,10 +2351,10 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E44" s="9" t="n">
         <v>9000000</v>
@@ -2450,79 +2367,79 @@
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>9000000</v>
+        <v>3360000</v>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>89.60%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L03</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>3360000</v>
+        <v>1920000</v>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>89.60%</t>
+          <t>80.00%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L03</t>
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>3340000</v>
+        <v>2400000</v>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>89.07%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
@@ -2533,20 +2450,20 @@
         <v>1</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1920000</v>
+        <v>2160000</v>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>90.00%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
@@ -2554,65 +2471,17 @@
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>2400000</v>
+        <v>2116000</v>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="n">
-        <v>175</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>2160000</v>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>90.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n">
-        <v>185</v>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
+          <t>88.17%</t>
         </is>
       </c>
     </row>

--- a/outputs/results/result2_filled.xlsx
+++ b/outputs/results/result2_filled.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1903,543 +1903,519 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>pattern_generation_time</t>
+          <t>problem1_pattern_generation_duration</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>94.71s</t>
+          <t>90.20s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>master_solve_time</t>
+          <t>problem1_master_solve_duration</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>94.78s</t>
+          <t>90.24s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>plotting_time_problem1</t>
+          <t>problem1_plotting_duration</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>9.72s</t>
+          <t>8.23s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>plotting_time_problem2</t>
+          <t>problem2_pattern_generation_duration</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>14.10s</t>
+          <t>87.19s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>problem2_master_solve_duration</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>87.24s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>problem2_plotting_duration</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>11.87s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
           <t>excel_writing_time</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>0.14s</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>0.10s</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Piece Production Quantities</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Piece</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Unit Volume</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Total Volume</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Unit Profit</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Total Profit</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>J01</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>1920000</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>620</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>18600</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>J02</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>780</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>23400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>J01</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>90000</v>
+        <v>64000</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>9000000</v>
+        <v>1920000</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>880</v>
+        <v>620</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>88000</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>J02</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2160000</v>
+        <v>2400000</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>1850</v>
+        <v>780</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>22200</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>J05</t>
+          <t>J03</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3840000</v>
+        <v>9000000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>2520</v>
+        <v>880</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>40320</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>J06</t>
+          <t>J04</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>362</v>
+        <v>12</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>100000</v>
+        <v>180000</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>36200000</v>
+        <v>2160000</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>1000</v>
+        <v>1850</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>362000</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>40320</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>J06</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>362</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>36200000</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>362000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>J07</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B35" s="9" t="n">
         <v>354</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C35" s="9" t="n">
         <v>48000</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D35" s="9" t="n">
         <v>16992000</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E35" s="9" t="n">
         <v>540</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F35" s="9" t="n">
         <v>191160</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Material Utilization Breakdown</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Unit Volume</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Total Volume</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Used Volume</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Waste</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Utilization</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>L02</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>18750000</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>16800000</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>89.60%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>L03</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C39" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>18750000</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>16800000</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>89.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="9" t="n">
         <v>2400000</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D41" s="9" t="n">
         <v>12000000</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E41" s="9" t="n">
         <v>10712000</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F41" s="9" t="n">
         <v>1288000</v>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>89.27%</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Pattern Usage Details</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Pattern ID</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Times Used</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Pieces</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Used Volume</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Utilization</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>3360000</v>
+        <v>9000000</v>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>89.60%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
-        <v>159</v>
+        <v>44</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>L03</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1920000</v>
+        <v>9000000</v>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>L03</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>2400000</v>
+        <v>3360000</v>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>89.60%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
@@ -2450,36 +2426,84 @@
         <v>1</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>2160000</v>
+        <v>1920000</v>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>90.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>90.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
         <v>229</v>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>L03</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C51" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D51" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>2116000</v>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>88.17%</t>
         </is>

--- a/outputs/results/result2_filled.xlsx
+++ b/outputs/results/result2_filled.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="computed_solution" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="computed_solution" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1518,16 +1518,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4">
         <f>C15*620+D15*780+E15*880+F15*1850+G15*2520+H15*1000+I15*540</f>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>2</v>
@@ -1582,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4">
         <f>C17*620+D17*780+E17*880+F17*1850+G17*2520+H17*1000+I17*540</f>
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="5" min="1" max="1"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>745680.00</t>
+          <t>748640.00</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>745,680.00</t>
+          <t>748,640.00</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>72,512,000</t>
+          <t>72,832,000</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>3,238,000</t>
+          <t>2,918,000</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>95.7254%</t>
+          <t>96.1479%</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>4.2746%</t>
+          <t>3.8521%</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>745,680.00</t>
+          <t>748,640.00</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>12.4981%</t>
+          <t>12.1508%</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.11</t>
         </is>
       </c>
     </row>
@@ -1896,616 +1896,525 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Runtime Breakdown</t>
+          <t>Piece Production Quantities</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>problem1_pattern_generation_duration</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>90.20s</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Unit Volume</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Total Volume</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Unit Profit</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>problem1_master_solve_duration</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>90.24s</t>
-        </is>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>J01</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>64000</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>18600</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>problem1_plotting_duration</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>8.23s</t>
-        </is>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>J02</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>23400</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>problem2_pattern_generation_duration</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>87.19s</t>
-        </is>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>J03</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>880</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>88000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>problem2_master_solve_duration</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>87.24s</t>
-        </is>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>J04</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>22200</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>problem2_plotting_duration</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>11.87s</t>
-        </is>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>J05</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>35280</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>excel_writing_time</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>0.10s</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Piece Production Quantities</t>
-        </is>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>J06</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>J07</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>16992000</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>540</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>191160</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Piece</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Material Utilization Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Unit Volume</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Total Volume</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Unit Profit</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Total Profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>J01</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>1920000</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>620</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>18600</v>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Waste</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>J02</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>80000</v>
+        <v>9000000</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2400000</v>
+        <v>45000000</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>780</v>
+        <v>45000000</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>23400</v>
+        <v>0</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>J03</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>90000</v>
+        <v>3750000</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>9000000</v>
+        <v>18750000</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>880</v>
+        <v>16800000</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>88000</v>
+        <v>1950000</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>89.60%</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>J04</t>
+          <t>L03</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>11032000</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>968000</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>91.93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Pattern Usage Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Pattern ID</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Times Used</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Pieces</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Used Volume</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>89.60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>179</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>187</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C32" s="9" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D32" s="9" t="n">
+      <c r="E41" s="9" t="n">
         <v>2160000</v>
       </c>
-      <c r="E32" s="9" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>22200</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>J05</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>3840000</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>2520</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>40320</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>J06</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n">
-        <v>362</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>36200000</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>362000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>J07</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>354</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>48000</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>16992000</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>540</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>191160</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Material Utilization Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Unit Volume</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Total Volume</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Used Volume</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Waste</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Utilization</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>L02</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>18750000</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>16800000</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>89.60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>90.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>256</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>L03</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>10712000</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>1288000</v>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>89.27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Pattern Usage Details</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Pattern ID</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Times Used</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Pieces</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Used Volume</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Utilization</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="n">
-        <v>129</v>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>L02</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>3360000</v>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>89.60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="n">
-        <v>159</v>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>1920000</v>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>80.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="n">
-        <v>167</v>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="n">
-        <v>189</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>2160000</v>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>90.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n">
-        <v>229</v>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>L03</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="n">
+      <c r="C42" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>2116000</v>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>88.17%</t>
+      <c r="D42" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>2276000</v>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>94.83%</t>
         </is>
       </c>
     </row>
